--- a/workspace/framework_paper/fp/gradient_fp_eval/gradient_fp_eval_times.xlsx
+++ b/workspace/framework_paper/fp/gradient_fp_eval/gradient_fp_eval_times.xlsx
@@ -448,19 +448,19 @@
         <v>0.5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.001413777489215136</v>
+        <v>0.001106218436034396</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001248221597634256</v>
+        <v>0.0009810000425204634</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001710138238267973</v>
+        <v>0.001347329046111554</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007148866372881457</v>
+        <v>0.0004556673974730075</v>
       </c>
       <c r="F2" t="n">
-        <v>2.803020060956478</v>
+        <v>1.614744230508804</v>
       </c>
     </row>
     <row r="3">
@@ -468,19 +468,19 @@
         <v>0.5210526315789473</v>
       </c>
       <c r="B3" t="n">
-        <v>0.001373968267580494</v>
+        <v>0.001092969119781628</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00123238914005924</v>
+        <v>0.0009552891622297466</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001705298374872655</v>
+        <v>0.001295143453171477</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0006427092012017965</v>
+        <v>0.0004336674755904824</v>
       </c>
       <c r="F3" t="n">
-        <v>2.820337651073933</v>
+        <v>1.713407080620527</v>
       </c>
     </row>
     <row r="4">
@@ -488,19 +488,19 @@
         <v>0.5421052631578948</v>
       </c>
       <c r="B4" t="n">
-        <v>0.001447882417123765</v>
+        <v>0.001040253333048895</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001352224949514493</v>
+        <v>0.0009203008422628045</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001806899911025539</v>
+        <v>0.001246879891259596</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0005995707743568346</v>
+        <v>0.0004231457808054984</v>
       </c>
       <c r="F4" t="n">
-        <v>2.987753646224737</v>
+        <v>1.765146588534117</v>
       </c>
     </row>
     <row r="5">
@@ -508,19 +508,19 @@
         <v>0.5631578947368421</v>
       </c>
       <c r="B5" t="n">
-        <v>0.00153689750470221</v>
+        <v>0.001108634173870087</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001380711700767279</v>
+        <v>0.001001142540480941</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001981522452551872</v>
+        <v>0.001381535727996379</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0007882616756251082</v>
+        <v>0.0004698191792704165</v>
       </c>
       <c r="F5" t="n">
-        <v>3.111202481240034</v>
+        <v>1.875252706259489</v>
       </c>
     </row>
     <row r="6">
@@ -528,19 +528,19 @@
         <v>0.5842105263157895</v>
       </c>
       <c r="B6" t="n">
-        <v>0.001515016602352261</v>
+        <v>0.00113381422823295</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001408079973771237</v>
+        <v>0.0009819191845599562</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001937737480038777</v>
+        <v>0.001349262516014278</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0006115041533485055</v>
+        <v>0.0004366758570540696</v>
       </c>
       <c r="F6" t="n">
-        <v>3.186009917408228</v>
+        <v>1.916745700836182</v>
       </c>
     </row>
     <row r="7">
@@ -548,19 +548,19 @@
         <v>0.6052631578947368</v>
       </c>
       <c r="B7" t="n">
-        <v>0.001618054184364155</v>
+        <v>0.001383686736226082</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001495189157431014</v>
+        <v>0.001192044283961877</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002034439947456121</v>
+        <v>0.001745447486173362</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008357342390809208</v>
+        <v>0.0005238524626474827</v>
       </c>
       <c r="F7" t="n">
-        <v>3.433950301259756</v>
+        <v>2.069817410707474</v>
       </c>
     </row>
     <row r="8">
@@ -568,19 +568,19 @@
         <v>0.6263157894736842</v>
       </c>
       <c r="B8" t="n">
-        <v>0.001703794156201184</v>
+        <v>0.001286541622830555</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001481279251165688</v>
+        <v>0.001062899131793529</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002172171670245007</v>
+        <v>0.00149103406118229</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0007085426151752472</v>
+        <v>0.0004619891790207476</v>
       </c>
       <c r="F8" t="n">
-        <v>3.449571636468172</v>
+        <v>2.146564075499773</v>
       </c>
     </row>
     <row r="9">
@@ -588,19 +588,19 @@
         <v>0.6473684210526316</v>
       </c>
       <c r="B9" t="n">
-        <v>0.001685048204381019</v>
+        <v>0.003093309862306342</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001607514187926427</v>
+        <v>0.002349184243939817</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002136508282274008</v>
+        <v>0.008274883250705897</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0005970175773836673</v>
+        <v>0.0004697133810259402</v>
       </c>
       <c r="F9" t="n">
-        <v>3.541561101078987</v>
+        <v>2.315141533762217</v>
       </c>
     </row>
     <row r="10">
@@ -608,19 +608,19 @@
         <v>0.6684210526315789</v>
       </c>
       <c r="B10" t="n">
-        <v>0.00173310502897948</v>
+        <v>0.001784052501898259</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001608933351235464</v>
+        <v>0.00165872170124203</v>
       </c>
       <c r="D10" t="n">
-        <v>0.002080455797258764</v>
+        <v>0.004232314028777182</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0006557850271929056</v>
+        <v>0.0005043141834903508</v>
       </c>
       <c r="F10" t="n">
-        <v>3.664311307370663</v>
+        <v>2.338768331557512</v>
       </c>
     </row>
     <row r="11">
@@ -628,19 +628,19 @@
         <v>0.6894736842105263</v>
       </c>
       <c r="B11" t="n">
-        <v>0.002673905896954239</v>
+        <v>0.00216375493328087</v>
       </c>
       <c r="C11" t="n">
-        <v>0.002425237527349964</v>
+        <v>0.002839954264927655</v>
       </c>
       <c r="D11" t="n">
-        <v>0.004512070778291672</v>
+        <v>0.01338846884784289</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0006175391474971547</v>
+        <v>0.0004425808240193874</v>
       </c>
       <c r="F11" t="n">
-        <v>3.760652349144221</v>
+        <v>2.578810232579708</v>
       </c>
     </row>
     <row r="12">
@@ -648,19 +648,19 @@
         <v>0.7105263157894737</v>
       </c>
       <c r="B12" t="n">
-        <v>0.003538795851636678</v>
+        <v>0.00821673404192552</v>
       </c>
       <c r="C12" t="n">
-        <v>0.003872359180240892</v>
+        <v>0.02497066914918833</v>
       </c>
       <c r="D12" t="n">
-        <v>0.004392845036927611</v>
+        <v>0.008066841565305367</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0005567099805921316</v>
+        <v>0.0004296774580143392</v>
       </c>
       <c r="F12" t="n">
-        <v>3.99679329380393</v>
+        <v>2.766005976498127</v>
       </c>
     </row>
     <row r="13">
@@ -668,19 +668,19 @@
         <v>0.7315789473684211</v>
       </c>
       <c r="B13" t="n">
-        <v>0.006770376580534503</v>
+        <v>0.005802852406632155</v>
       </c>
       <c r="C13" t="n">
-        <v>0.008250817622756585</v>
+        <v>0.007977541686268524</v>
       </c>
       <c r="D13" t="n">
-        <v>0.004082048421259969</v>
+        <v>0.01891920214984566</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0006890892185037956</v>
+        <v>0.0004195941216312349</v>
       </c>
       <c r="F13" t="n">
-        <v>4.327445442378521</v>
+        <v>3.069787151366472</v>
       </c>
     </row>
     <row r="14">
@@ -688,19 +688,19 @@
         <v>0.7526315789473684</v>
       </c>
       <c r="B14" t="n">
-        <v>0.009630310017964803</v>
+        <v>0.02233054786338471</v>
       </c>
       <c r="C14" t="n">
-        <v>0.01281959409883712</v>
+        <v>0.04122281224699691</v>
       </c>
       <c r="D14" t="n">
-        <v>0.009498720722040161</v>
+        <v>0.009960748311132193</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0004980457987403497</v>
+        <v>0.0003882149758283049</v>
       </c>
       <c r="F14" t="n">
-        <v>4.719483923316002</v>
+        <v>3.528094295710325</v>
       </c>
     </row>
     <row r="15">
@@ -708,19 +708,19 @@
         <v>0.7736842105263158</v>
       </c>
       <c r="B15" t="n">
-        <v>0.01977909972774796</v>
+        <v>0.02957377720740624</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04857965365285054</v>
+        <v>0.05603514824761078</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01611670651473105</v>
+        <v>0.02016232100198977</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0005625466769561172</v>
+        <v>0.0004056942381430418</v>
       </c>
       <c r="F15" t="n">
-        <v>5.435090338140726</v>
+        <v>3.941994597315788</v>
       </c>
     </row>
     <row r="16">
@@ -728,19 +728,19 @@
         <v>0.7947368421052632</v>
       </c>
       <c r="B16" t="n">
-        <v>0.05447343833744526</v>
+        <v>0.05845858836895786</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1120722926978488</v>
+        <v>0.09516418219543993</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0194647990190424</v>
+        <v>0.02121734679676592</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0004869667562888935</v>
+        <v>0.0003706858633086085</v>
       </c>
       <c r="F16" t="n">
-        <v>6.018126690685749</v>
+        <v>4.457771845906973</v>
       </c>
     </row>
     <row r="17">
@@ -748,19 +748,19 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1097581230464857</v>
+        <v>0.1078659919032361</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2500932800670853</v>
+        <v>0.2831902671547141</v>
       </c>
       <c r="D17" t="n">
-        <v>0.02480743976542726</v>
+        <v>0.03174819166539237</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0004713017208268866</v>
+        <v>0.0003655000193975866</v>
       </c>
       <c r="F17" t="n">
-        <v>6.911015069782734</v>
+        <v>5.470394557863474</v>
       </c>
     </row>
     <row r="18">
@@ -768,19 +768,19 @@
         <v>0.8368421052631578</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1984118271875195</v>
+        <v>0.1939191761752591</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4611711517360527</v>
+        <v>0.3956207267986611</v>
       </c>
       <c r="D18" t="n">
-        <v>0.04527668676455505</v>
+        <v>0.05777255582506768</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0003574774583103135</v>
+        <v>0.0003283766272943467</v>
       </c>
       <c r="F18" t="n">
-        <v>7.764483018517494</v>
+        <v>5.962164504230023</v>
       </c>
     </row>
     <row r="19">
@@ -788,19 +788,19 @@
         <v>0.8578947368421053</v>
       </c>
       <c r="B19" t="n">
-        <v>0.3122263127053156</v>
+        <v>0.2492050138837658</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6649956467957235</v>
+        <v>0.5239891266368795</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0579281536443159</v>
+        <v>0.07519941070466302</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0003677040804177523</v>
+        <v>0.0002974833233747631</v>
       </c>
       <c r="F19" t="n">
-        <v>8.83447860777378</v>
+        <v>6.997778120189905</v>
       </c>
     </row>
     <row r="20">
@@ -808,19 +808,19 @@
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="n">
-        <v>0.455866144800093</v>
+        <v>0.5097871224535629</v>
       </c>
       <c r="C20" t="n">
-        <v>1.052560932296328</v>
+        <v>0.9674434129707515</v>
       </c>
       <c r="D20" t="n">
-        <v>0.08134783892426639</v>
+        <v>0.106878782811109</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0004389216570416466</v>
+        <v>0.0002645350468810648</v>
       </c>
       <c r="F20" t="n">
-        <v>9.776215092837811</v>
+        <v>9.327774233072995</v>
       </c>
     </row>
     <row r="21">
@@ -828,19 +828,19 @@
         <v>0.9</v>
       </c>
       <c r="B21" t="n">
-        <v>0.6984298436506652</v>
+        <v>0.8418229811906349</v>
       </c>
       <c r="C21" t="n">
-        <v>1.402622971304227</v>
+        <v>1.736725462258328</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1270808809506707</v>
+        <v>0.1621195363055449</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0004125407198444009</v>
+        <v>0.0002311617264058441</v>
       </c>
       <c r="F21" t="n">
-        <v>11.00750870227814</v>
+        <v>11.06285358965397</v>
       </c>
     </row>
   </sheetData>

--- a/workspace/framework_paper/fp/gradient_fp_eval/gradient_fp_eval_times.xlsx
+++ b/workspace/framework_paper/fp/gradient_fp_eval/gradient_fp_eval_times.xlsx
@@ -448,19 +448,19 @@
         <v>0.5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.001106218436034396</v>
+        <v>0.001099896678933874</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0009810000425204634</v>
+        <v>0.0009372807131148874</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001347329046111554</v>
+        <v>0.00121252330369316</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0004556673974730075</v>
+        <v>0.0003898808604571968</v>
       </c>
       <c r="F2" t="n">
-        <v>1.614744230508804</v>
+        <v>0.5709892903268338</v>
       </c>
     </row>
     <row r="3">
@@ -468,19 +468,19 @@
         <v>0.5210526315789473</v>
       </c>
       <c r="B3" t="n">
-        <v>0.001092969119781628</v>
+        <v>0.001198643443640321</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009552891622297466</v>
+        <v>0.001041068398626521</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001295143453171477</v>
+        <v>0.00151529737515375</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0004336674755904824</v>
+        <v>0.0004215190815739333</v>
       </c>
       <c r="F3" t="n">
-        <v>1.713407080620527</v>
+        <v>0.6259903608262539</v>
       </c>
     </row>
     <row r="4">
@@ -488,19 +488,19 @@
         <v>0.5421052631578948</v>
       </c>
       <c r="B4" t="n">
-        <v>0.001040253333048895</v>
+        <v>0.001254161630058661</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0009203008422628045</v>
+        <v>0.001110290721990168</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001246879891259596</v>
+        <v>0.001492769143078476</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0004231457808054984</v>
+        <v>0.0005129258113447577</v>
       </c>
       <c r="F4" t="n">
-        <v>1.765146588534117</v>
+        <v>0.6294843511283398</v>
       </c>
     </row>
     <row r="5">
@@ -508,19 +508,19 @@
         <v>0.5631578947368421</v>
       </c>
       <c r="B5" t="n">
-        <v>0.001108634173870087</v>
+        <v>0.001197830853052437</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001001142540480941</v>
+        <v>0.00105851917527616</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001381535727996379</v>
+        <v>0.001431979954941198</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0004698191792704165</v>
+        <v>0.0004535508959088474</v>
       </c>
       <c r="F5" t="n">
-        <v>1.875252706259489</v>
+        <v>0.6433845806121826</v>
       </c>
     </row>
     <row r="6">
@@ -528,19 +528,19 @@
         <v>0.5842105263157895</v>
       </c>
       <c r="B6" t="n">
-        <v>0.00113381422823295</v>
+        <v>0.001250870805233717</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009819191845599562</v>
+        <v>0.001112818325636909</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001349262516014278</v>
+        <v>0.001479770840378478</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0004366758570540696</v>
+        <v>0.0004605699214152992</v>
       </c>
       <c r="F6" t="n">
-        <v>1.916745700836182</v>
+        <v>0.746490034610033</v>
       </c>
     </row>
     <row r="7">
@@ -548,19 +548,19 @@
         <v>0.6052631578947368</v>
       </c>
       <c r="B7" t="n">
-        <v>0.001383686736226082</v>
+        <v>0.00133532419684343</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001192044283961877</v>
+        <v>0.001250666765263304</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001745447486173362</v>
+        <v>0.001700286722043529</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0005238524626474827</v>
+        <v>0.0005404108599759639</v>
       </c>
       <c r="F7" t="n">
-        <v>2.069817410707474</v>
+        <v>0.8117360903322697</v>
       </c>
     </row>
     <row r="8">
@@ -568,19 +568,19 @@
         <v>0.6263157894736842</v>
       </c>
       <c r="B8" t="n">
-        <v>0.001286541622830555</v>
+        <v>0.001676240055821836</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001062899131793529</v>
+        <v>0.001795003336155787</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00149103406118229</v>
+        <v>0.001983577546197921</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0004619891790207476</v>
+        <v>0.0004519799037370831</v>
       </c>
       <c r="F8" t="n">
-        <v>2.146564075499773</v>
+        <v>1.128321632444859</v>
       </c>
     </row>
     <row r="9">
@@ -588,19 +588,19 @@
         <v>0.6473684210526316</v>
       </c>
       <c r="B9" t="n">
-        <v>0.003093309862306342</v>
+        <v>0.001654027493204922</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002349184243939817</v>
+        <v>0.001895915016066283</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008274883250705897</v>
+        <v>0.002114666613051668</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0004697133810259402</v>
+        <v>0.0004698832880239934</v>
       </c>
       <c r="F9" t="n">
-        <v>2.315141533762217</v>
+        <v>1.286375274509191</v>
       </c>
     </row>
     <row r="10">
@@ -608,19 +608,19 @@
         <v>0.6684210526315789</v>
       </c>
       <c r="B10" t="n">
-        <v>0.001784052501898259</v>
+        <v>0.00198485744302161</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00165872170124203</v>
+        <v>0.00257868166663684</v>
       </c>
       <c r="D10" t="n">
-        <v>0.004232314028777182</v>
+        <v>0.002874965782975778</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0005043141834903508</v>
+        <v>0.0004796558152884245</v>
       </c>
       <c r="F10" t="n">
-        <v>2.338768331557512</v>
+        <v>1.398834803849459</v>
       </c>
     </row>
     <row r="11">
@@ -628,19 +628,19 @@
         <v>0.6894736842105263</v>
       </c>
       <c r="B11" t="n">
-        <v>0.00216375493328087</v>
+        <v>0.002838161722756922</v>
       </c>
       <c r="C11" t="n">
-        <v>0.002839954264927655</v>
+        <v>0.003371764967450872</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01338846884784289</v>
+        <v>0.002052275846945122</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0004425808240193874</v>
+        <v>0.0003973841015249491</v>
       </c>
       <c r="F11" t="n">
-        <v>2.578810232579708</v>
+        <v>1.630984642058611</v>
       </c>
     </row>
     <row r="12">
@@ -648,19 +648,19 @@
         <v>0.7105263157894737</v>
       </c>
       <c r="B12" t="n">
-        <v>0.00821673404192552</v>
+        <v>0.003556827605934813</v>
       </c>
       <c r="C12" t="n">
-        <v>0.02497066914918833</v>
+        <v>0.004927404162008315</v>
       </c>
       <c r="D12" t="n">
-        <v>0.008066841565305367</v>
+        <v>0.003341178330592811</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0004296774580143392</v>
+        <v>0.0005005384050309658</v>
       </c>
       <c r="F12" t="n">
-        <v>2.766005976498127</v>
+        <v>1.976193261444569</v>
       </c>
     </row>
     <row r="13">
@@ -668,19 +668,19 @@
         <v>0.7315789473684211</v>
       </c>
       <c r="B13" t="n">
-        <v>0.005802852406632155</v>
+        <v>0.00868806738872081</v>
       </c>
       <c r="C13" t="n">
-        <v>0.007977541686268524</v>
+        <v>0.01158929589320905</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01891920214984566</v>
+        <v>0.0235715248377528</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0004195941216312349</v>
+        <v>0.0004318499972578138</v>
       </c>
       <c r="F13" t="n">
-        <v>3.069787151366472</v>
+        <v>2.342407350838184</v>
       </c>
     </row>
     <row r="14">
@@ -688,19 +688,19 @@
         <v>0.7526315789473684</v>
       </c>
       <c r="B14" t="n">
-        <v>0.02233054786338471</v>
+        <v>0.0327541687618941</v>
       </c>
       <c r="C14" t="n">
-        <v>0.04122281224699691</v>
+        <v>0.07462747341953219</v>
       </c>
       <c r="D14" t="n">
-        <v>0.009960748311132193</v>
+        <v>0.02232289996813051</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0003882149758283049</v>
+        <v>0.0003666382608935237</v>
       </c>
       <c r="F14" t="n">
-        <v>3.528094295710325</v>
+        <v>2.904029214084149</v>
       </c>
     </row>
     <row r="15">
@@ -708,19 +708,19 @@
         <v>0.7736842105263158</v>
       </c>
       <c r="B15" t="n">
-        <v>0.02957377720740624</v>
+        <v>0.03871727414429188</v>
       </c>
       <c r="C15" t="n">
-        <v>0.05603514824761078</v>
+        <v>0.100277218145784</v>
       </c>
       <c r="D15" t="n">
-        <v>0.02016232100198977</v>
+        <v>0.03267918783822097</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0004056942381430418</v>
+        <v>0.0003050600213464349</v>
       </c>
       <c r="F15" t="n">
-        <v>3.941994597315788</v>
+        <v>3.711354681700468</v>
       </c>
     </row>
     <row r="16">
@@ -728,19 +728,19 @@
         <v>0.7947368421052632</v>
       </c>
       <c r="B16" t="n">
-        <v>0.05845858836895786</v>
+        <v>0.0455742691620253</v>
       </c>
       <c r="C16" t="n">
-        <v>0.09516418219543993</v>
+        <v>0.1369705143303145</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02121734679676592</v>
+        <v>0.0414993869070895</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0003706858633086085</v>
+        <v>0.0003279216354712844</v>
       </c>
       <c r="F16" t="n">
-        <v>4.457771845906973</v>
+        <v>4.232722194939852</v>
       </c>
     </row>
     <row r="17">
@@ -748,19 +748,19 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1078659919032361</v>
+        <v>0.1117917700461112</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2831902671547141</v>
+        <v>0.2943682548729703</v>
       </c>
       <c r="D17" t="n">
-        <v>0.03174819166539237</v>
+        <v>0.04701554742758162</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0003655000193975866</v>
+        <v>0.0002979473990853876</v>
       </c>
       <c r="F17" t="n">
-        <v>5.470394557863474</v>
+        <v>4.853463417589665</v>
       </c>
     </row>
     <row r="18">
@@ -768,19 +768,19 @@
         <v>0.8368421052631578</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1939191761752591</v>
+        <v>0.2270160537248012</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3956207267986611</v>
+        <v>0.5419091231643688</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05777255582506768</v>
+        <v>0.05373483163770288</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0003283766272943467</v>
+        <v>0.0002733257424551994</v>
       </c>
       <c r="F18" t="n">
-        <v>5.962164504230023</v>
+        <v>6.16642532736063</v>
       </c>
     </row>
     <row r="19">
@@ -788,19 +788,19 @@
         <v>0.8578947368421053</v>
       </c>
       <c r="B19" t="n">
-        <v>0.2492050138837658</v>
+        <v>0.3340643201500643</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5239891266368795</v>
+        <v>0.7246027179120574</v>
       </c>
       <c r="D19" t="n">
-        <v>0.07519941070466302</v>
+        <v>0.07965744178276508</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0002974833233747631</v>
+        <v>0.0002609924983698875</v>
       </c>
       <c r="F19" t="n">
-        <v>6.997778120189905</v>
+        <v>7.975978903323412</v>
       </c>
     </row>
     <row r="20">
@@ -808,19 +808,19 @@
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="n">
-        <v>0.5097871224535629</v>
+        <v>0.5673565821803641</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9674434129707515</v>
+        <v>1.130395688795252</v>
       </c>
       <c r="D20" t="n">
-        <v>0.106878782811109</v>
+        <v>0.1269999901019037</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0002645350468810648</v>
+        <v>0.0002348466252442449</v>
       </c>
       <c r="F20" t="n">
-        <v>9.327774233072995</v>
+        <v>9.580737360864878</v>
       </c>
     </row>
     <row r="21">
@@ -828,19 +828,19 @@
         <v>0.9</v>
       </c>
       <c r="B21" t="n">
-        <v>0.8418229811906349</v>
+        <v>0.8468291002919431</v>
       </c>
       <c r="C21" t="n">
-        <v>1.736725462258328</v>
+        <v>1.878337213947671</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1621195363055449</v>
+        <v>0.1612141921231523</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0002311617264058441</v>
+        <v>0.0002119066228624433</v>
       </c>
       <c r="F21" t="n">
-        <v>11.06285358965397</v>
+        <v>12.1309246443212</v>
       </c>
     </row>
   </sheetData>
